--- a/artfynd/A 22229-2024 artfynd.xlsx
+++ b/artfynd/A 22229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6969392</v>
+        <v>6969361</v>
       </c>
       <c r="B7" t="n">
-        <v>95591</v>
+        <v>95594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222112</v>
+        <v>165</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(S. G. Gmel.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541033.5644703099</v>
+        <v>541027.7542085554</v>
       </c>
       <c r="R7" t="n">
-        <v>6871028.704347452</v>
+        <v>6871041.803435897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rätt många år sedan jag senast såg månlåsbräken här</t>
+          <t>Ingen topplåsbräken funnen. Sågs senast i kattfottuva i vägens mittsträng. Torpet används inte och det körs knappt något på vägen, dessutom växer skog på båda sidor om vägen och det blir allt mer skuggigt. Dessförinnan växte den ett par meter in från vägen vid ett fd timmeravlägg bland kattfot där det nu är röjd tallskog, kattfoten finns kvar, men det är igenväxt med lingon.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Öppet i tallskog på sandig mark</t>
+          <t>Mittsträng av väg i tallskog på sandig mark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6969361</v>
+        <v>89180194</v>
       </c>
       <c r="B8" t="n">
-        <v>95594</v>
+        <v>95591</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,41 +1419,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>165</v>
+        <v>222112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Topplåsbräken</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Botrychium lanceolatum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjurstorpet, vid infart från Opplivägen, Hls</t>
+          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541027.7542085554</v>
+        <v>541014.2891543055</v>
       </c>
       <c r="R8" t="n">
-        <v>6871041.803435897</v>
+        <v>6871025.650008361</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,7 +1481,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1487,7 +1491,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1495,44 +1499,35 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ingen topplåsbräken funnen. Sågs senast i kattfottuva i vägens mittsträng. Torpet används inte och det körs knappt något på vägen, dessutom växer skog på båda sidor om vägen och det blir allt mer skuggigt. Dessförinnan växte den ett par meter in från vägen vid ett fd timmeravlägg bland kattfot där det nu är röjd tallskog, kattfoten finns kvar, men det är igenväxt med lingon.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Mittsträng av väg i tallskog på sandig mark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89180194</v>
+        <v>89180205</v>
       </c>
       <c r="B9" t="n">
-        <v>95591</v>
+        <v>95594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,25 +1536,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222112</v>
+        <v>165</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(S. G. Gmel.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1644,123 +1639,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>89180205</v>
-      </c>
-      <c r="B10" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>165</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Botrychium lanceolatum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>541014.2891543055</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6871025.650008361</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22229-2024 artfynd.xlsx
+++ b/artfynd/A 22229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4543922</v>
+        <v>89180205</v>
       </c>
       <c r="B2" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(S. G. Gmel.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oppli, Bjurstorpet (Skölds), Hls</t>
+          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540958.5461238172</v>
+        <v>541014</v>
       </c>
       <c r="R2" t="n">
-        <v>6871039.08841923</v>
+        <v>6871026</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,102 +744,87 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Östra sidan av fd lada(?). Igenväxt med tjock mossa och nästan heltäckande lingon</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På numera oanvänd infart till fd lada(?)</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>192840</v>
+        <v>6969390</v>
       </c>
       <c r="B3" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Topplåsbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lanceolatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oppli, Bjurstorpet (Skölds), infartsvägen, Hls</t>
+          <t>Bjurstorpet, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541020.859912216</v>
+        <v>540948</v>
       </c>
       <c r="R3" t="n">
-        <v>6871027.610520651</v>
+        <v>6871052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,31 +851,16 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Infart till torp från Opplivägen. I större tuva med kattfot på vägens mittsträng. Ej sedd på några år, sedd 2005. Först sedd vid sidan om vägen där man haft ett timmeravlägg vid avverkning, där ungskogen gallrades ifjol. Dök sedan upp på mittsträngen.</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -901,7 +870,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sandig jord. Mittsträng av väg bland kattfot.</t>
+          <t>Hjulspår i knappt använd bilväg till torp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>238952</v>
+        <v>89180194</v>
       </c>
       <c r="B4" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,37 +899,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>167</v>
+        <v>222112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oppli, Bjurstorpet (Skölds), Hls</t>
+          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540958.5461238172</v>
+        <v>541014</v>
       </c>
       <c r="R4" t="n">
-        <v>6871039.08841923</v>
+        <v>6871026</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,67 +957,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Östra sidan av fd lada(?). Igenväxt med tjock mossa och nästan heltäckande lingon. En liten planta upptäckt 1984, sedd ett antal år därefter, men nu utgången sedan länge.</t>
+          <t>1993-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På numera oanvänd infart till fd lada(?)</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Erling Jirle</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4543923</v>
+        <v>6969393</v>
       </c>
       <c r="B5" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1001,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222112</v>
+        <v>222929</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Backruta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Thalictrum simplex</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oppli, Bjurstorpet (Skölds), intill infartsvägen, Hls</t>
+          <t>Bjurstorpet, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541032.622552129</v>
+        <v>540942</v>
       </c>
       <c r="R5" t="n">
-        <v>6871028.692989652</v>
+        <v>6871050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,31 +1060,16 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Några meter från Opplivägen, vägskäl väg in mot Bjurstorpet. Trots gallring av ungtallskogen ifjol och det nu är rätt öppet fanns inga låsbräknar. Ifjol tog jag bort de minde träden som fällts över platsen.</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
@@ -1145,7 +1079,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gallrad ungtallskog, sandig jord, nära litet vägskäl</t>
+          <t>Ängsmark mellan bilväg och fd åker</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1160,484 +1094,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>192839</v>
-      </c>
-      <c r="B6" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>165</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Botrychium lanceolatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Oppli, Bjurstorpet (Skölds), Hls</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>540958.5461238172</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6871039.08841923</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2011-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Östra sidan av fd lada(?). Igenväxt med tjock mossa och nästan heltäckande lingon. På vägen drygt halvmeterhöga tallar. Upptäckt 1984, ej sedd på många år. Senast väst ladan, där nu en mindre virkeshög. Ansåg växtplatserna vid ladan utgångna redan 2002.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>På numera oanvänd infart till fd lada(?)</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6969361</v>
-      </c>
-      <c r="B7" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>165</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Botrychium lanceolatum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bjurstorpet, vid infart från Opplivägen, Hls</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>541027.7542085554</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6871041.803435897</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ingen topplåsbräken funnen. Sågs senast i kattfottuva i vägens mittsträng. Torpet används inte och det körs knappt något på vägen, dessutom växer skog på båda sidor om vägen och det blir allt mer skuggigt. Dessförinnan växte den ett par meter in från vägen vid ett fd timmeravlägg bland kattfot där det nu är röjd tallskog, kattfoten finns kvar, men det är igenväxt med lingon.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Mittsträng av väg i tallskog på sandig mark</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>89180194</v>
-      </c>
-      <c r="B8" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>222112</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Månlåsbräken</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>541014.2891543055</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6871025.650008361</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>89180205</v>
-      </c>
-      <c r="B9" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>165</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Topplåsbräken</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Botrychium lanceolatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Oppli, låsbräkenrutor (Bengt Stridhs), Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>541014.2891543055</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6871025.650008361</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>1993-07-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erling Jirle</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22229-2024 artfynd.xlsx
+++ b/artfynd/A 22229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89180205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6969390</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89180194</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,8 +1114,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6969393</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>